--- a/out/data_excel.xlsx
+++ b/out/data_excel.xlsx
@@ -12,45 +12,63 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t xml:space="preserve">Группа	Возраст	Пол	Рост	Группа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">крови	Базофилы_E1	Эозинофилы_E1	Гемоглобин_E1	Эритроциты_E1	Базофилы_E2	Эозинофилы_E2	Гемоглобин_E2	Эритроциты_E2</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve">Группа</t>
   </si>
   <si>
-    <t xml:space="preserve">1	31	Женский	174	A (II)	0.4222	0.6465	10.6842	4.2573	0.8264	1.6613	11.4051	6.5728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1	28	Женский	157	A (II)	0.327	4.9742	9.6169	3.8813	0.7312	5.989	10.3378	6.1968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1	33	Женский	166	NA	0.7994	3.3875	10.1628	5.0607	1.2036	4.4023	10.8837	7.3762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1	26	Женский	168	O (I)	0.0237	4.5403	10.6391	3.8083	0.4279	5.5551	11.36	6.1238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1	33	Женский	170	A (II)	0.6636	3.3159	12.259	3.0321	1.0678	4.3307	12.9799	5.3476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1	28	Мужской	172	B (III)	0.481	2.7863	12.3529	4.7917	0.8852	3.8011	13.0738	7.1072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1	27	Мужской	157	A (II)	0.8899	2.3432	11.2656	3.3619	1.2941	3.358	11.9865	5.6774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1	31	Мужской	174	NA	0.8576	3.9788	14.8948	4.4598	1.2618	4.9936	15.6157	6.7753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1	23	Женский	175	A (II)	0.3832	3.3896	15.6802	4.4339	0.7874	4.4044	16.4011	6.7494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1	29	Женский	172	A (II)	0.2812	7.9352	12.9084	4.3275	0.6854	8.95	13.6293	6.643</t>
+    <t xml:space="preserve">Возраст</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пол</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рост</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Группа крови</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Базофилы_E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эозинофилы_E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гемоглобин_E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эритроциты_E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Базофилы_E2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эозинофилы_E2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гемоглобин_E2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эритроциты_E2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Группа 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Женский</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A (II)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O (I)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мужской</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B (III)</t>
   </si>
 </sst>
 </file>
@@ -386,85 +404,444 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+        <v>13</v>
+      </c>
+      <c r="B2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="n">
+        <v>174</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10.6842</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.2573</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8264</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.6613</v>
+      </c>
+      <c r="L2" t="n">
+        <v>11.4051</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6.5728</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
+        <v>13</v>
+      </c>
+      <c r="B3" t="n">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>157</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.9742</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9.6169</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.8813</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7312</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.989</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10.3378</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6.1968</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
+        <v>13</v>
+      </c>
+      <c r="B4" t="n">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="n">
+        <v>166</v>
+      </c>
+      <c r="E4"/>
+      <c r="F4" t="n">
+        <v>0.7994</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.3875</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10.1628</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.0607</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.2036</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.4023</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10.8837</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7.3762</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
+        <v>13</v>
+      </c>
+      <c r="B5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="n">
+        <v>168</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.5403</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10.6391</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.8083</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.5551</v>
+      </c>
+      <c r="L5" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6.1238</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
+        <v>13</v>
+      </c>
+      <c r="B6" t="n">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="n">
+        <v>170</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6636</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.3159</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12.259</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.0321</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.0678</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.3307</v>
+      </c>
+      <c r="L6" t="n">
+        <v>12.9799</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5.3476</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="B7" t="n">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="n">
+        <v>172</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.7863</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12.3529</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.7917</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8852</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.8011</v>
+      </c>
+      <c r="L7" t="n">
+        <v>13.0738</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7.1072</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
+        <v>13</v>
+      </c>
+      <c r="B8" t="n">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="n">
+        <v>157</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8899</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.3432</v>
+      </c>
+      <c r="H8" t="n">
+        <v>11.2656</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.3619</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.2941</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="L8" t="n">
+        <v>11.9865</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5.6774</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="B9" t="n">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="n">
+        <v>174</v>
+      </c>
+      <c r="E9"/>
+      <c r="F9" t="n">
+        <v>0.8576</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.9788</v>
+      </c>
+      <c r="H9" t="n">
+        <v>14.8948</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.4598</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.2618</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.9936</v>
+      </c>
+      <c r="L9" t="n">
+        <v>15.6157</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6.7753</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="B10" t="n">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="n">
+        <v>175</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.3896</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15.6802</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.4339</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7874</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.4044</v>
+      </c>
+      <c r="L10" t="n">
+        <v>16.4011</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6.7494</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B11" t="n">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="n">
+        <v>172</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7.9352</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12.9084</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.3275</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6854</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.95</v>
+      </c>
+      <c r="L11" t="n">
+        <v>13.6293</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6.643</v>
       </c>
     </row>
   </sheetData>
